--- a/output/laminas_comunales/comunal_o_ocup_a_2022_maule.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2022_maule.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C246"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,37 +384,37 @@
         </is>
       </c>
       <c r="C2">
-        <v>41.2071766362225</v>
+        <v>59.6353905963226</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Romeral</t>
+          <t>Sagrada Familia</t>
         </is>
       </c>
       <c r="C3">
-        <v>39.7961608397388</v>
+        <v>58.9435979076643</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sagrada Familia</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="C4">
-        <v>39.7144623468954</v>
+        <v>58.6414735924265</v>
       </c>
     </row>
     <row r="5">
@@ -429,37 +429,37 @@
         </is>
       </c>
       <c r="C5">
-        <v>39.2281682576109</v>
+        <v>58.2798648564875</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Curicó</t>
         </is>
       </c>
       <c r="C6">
-        <v>38.8419232927353</v>
+        <v>58.1110638764708</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>Romeral</t>
         </is>
       </c>
       <c r="C7">
-        <v>38.3006713148871</v>
+        <v>57.2561340514662</v>
       </c>
     </row>
     <row r="8">
@@ -474,7 +474,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>38.2399329686037</v>
+        <v>56.8517951856385</v>
       </c>
     </row>
     <row r="9">
@@ -489,202 +489,202 @@
         </is>
       </c>
       <c r="C9">
-        <v>38.1885199702816</v>
+        <v>56.408393248687</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>San Rafael</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="C10">
-        <v>36.9818732986884</v>
+        <v>56.3904195645077</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Constitución</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="C11">
-        <v>36.6994812544211</v>
+        <v>56.3300430270818</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Linares</t>
+          <t>Villa Alegre</t>
         </is>
       </c>
       <c r="C12">
-        <v>36.2021827161606</v>
+        <v>55.9272300469484</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rauco</t>
+          <t>Linares</t>
         </is>
       </c>
       <c r="C13">
-        <v>35.5151220215565</v>
+        <v>55.8532246315907</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>San Javier</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="C14">
-        <v>34.7511156056374</v>
+        <v>55.3130358807843</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pelarco</t>
+          <t>San Rafael</t>
         </is>
       </c>
       <c r="C15">
-        <v>34.0322137509444</v>
+        <v>54.6543834296724</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Villa Alegre</t>
+          <t>Rauco</t>
         </is>
       </c>
       <c r="C16">
-        <v>33.9559579700425</v>
+        <v>54.3785952164699</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pencahue</t>
+          <t>Constitución</t>
         </is>
       </c>
       <c r="C17">
-        <v>33.9435146443515</v>
+        <v>54.0432287570276</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>San Clemente</t>
+          <t>San Javier</t>
         </is>
       </c>
       <c r="C18">
-        <v>33.7219560327455</v>
+        <v>53.5541954078824</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Colbún</t>
+          <t>Pelarco</t>
         </is>
       </c>
       <c r="C19">
-        <v>33.6058972141682</v>
+        <v>53.4456140350877</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Yerbas Buenas</t>
+          <t>Linares</t>
         </is>
       </c>
       <c r="C20">
-        <v>33.3777596588058</v>
+        <v>52.7657020740936</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Longaví</t>
+          <t>Curicó</t>
         </is>
       </c>
       <c r="C21">
-        <v>31.9831787627754</v>
+        <v>52.4186887458576</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Parral</t>
+          <t>Yerbas Buenas</t>
         </is>
       </c>
       <c r="C22">
-        <v>31.1661280490351</v>
+        <v>51.6876552728519</v>
       </c>
     </row>
     <row r="23">
@@ -699,127 +699,3352 @@
         </is>
       </c>
       <c r="C23">
-        <v>30.1610135271553</v>
+        <v>51.3782484602674</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Retiro</t>
+          <t>Colbún</t>
         </is>
       </c>
       <c r="C24">
-        <v>30.0704572869832</v>
+        <v>51.1642775422303</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Empedrado</t>
+          <t>Sagrada Familia</t>
         </is>
       </c>
       <c r="C25">
-        <v>29.8723536737235</v>
+        <v>51.0831788693234</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Licantén</t>
+          <t>San Clemente</t>
         </is>
       </c>
       <c r="C26">
-        <v>29.1957395073475</v>
+        <v>50.963968579235</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
+          <t>Pencahue</t>
         </is>
       </c>
       <c r="C27">
-        <v>28.8803299699793</v>
+        <v>50.7667286245353</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Curepto</t>
+          <t>Molina</t>
         </is>
       </c>
       <c r="C28">
-        <v>27.2849462365591</v>
+        <v>50.7385885127169</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chanco</t>
+          <t>Romeral</t>
         </is>
       </c>
       <c r="C29">
-        <v>24.7991468919535</v>
+        <v>50.4323804948355</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>7103</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vichuquén</t>
+          <t>Curepto</t>
         </is>
       </c>
       <c r="C30">
-        <v>24.6712158808933</v>
+        <v>50.1593806921676</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>50.0847199976271</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>50.0252282005413</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>7403</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Longaví</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>49.6855749486653</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>49.457643754019</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Empedrado</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>48.7631027253669</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>48.44057780696</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>48.0357077323939</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>7108</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Río Claro</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>47.6543914739747</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>47.2964225948028</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>7308</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Teno</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>47.2572557362103</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>47.0202622169249</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>46.8610955318751</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>46.0870202377633</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>46.0250198804229</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>7307</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>45.9948320413437</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>7304</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Molina</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>45.7075487363422</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>7108</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Río Claro</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>45.6736596736597</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>45.4541118107231</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>7305</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Rauco</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>45.2685145084452</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>7306</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Romeral</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>45.2469793887704</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>7110</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>45.1151560178306</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>7308</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Teno</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>44.8713583049565</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>44.8632112139221</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>San Javier</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>44.8114458030951</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Pencahue</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>44.5984437960261</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>44.5921660538986</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>44.5257696992122</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>7110</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>44.3285433979686</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>44.0117032832265</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>43.8838280158527</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>43.5236187614755</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>43.1464254533123</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>43.1015056717025</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Colbún</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>43.0361675126904</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Vichuquén</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>42.672741078208</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Villa Alegre</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>42.4330538274276</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>7109</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>San Clemente</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>42.3591851558373</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>San Javier</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>41.9523809523809</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Colbún</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>41.9036014080693</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>41.8205482285253</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>7109</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>San Clemente</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>41.7970218539041</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Pelarco</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>41.660084254871</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Villa Alegre</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>41.3284632034632</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>7305</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Rauco</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>41.2121212121212</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>41.2071766362225</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>7408</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Yerbas Buenas</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>41.0510772814242</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>40.5891102808911</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>40.3444503509218</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>7408</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Yerbas Buenas</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>40.0955175427644</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Chanco</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>39.9527806925498</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>7306</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Romeral</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>39.7961608397388</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>7307</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>39.7144623468954</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>7302</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Hualañé</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>39.7034764826176</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Pelarco</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>39.6263472276328</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>39.5028816281199</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>39.2971770822853</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>7304</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Molina</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>39.2281682576109</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>39.0174617004284</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>38.8419232927353</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Pencahue</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>38.6926512383272</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>38.3006713148871</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>7108</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Río Claro</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>38.2399329686037</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>7308</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Teno</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>38.1885199702816</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>7403</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Longaví</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>37.9122402832885</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>37.7133290127457</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>7403</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Longaví</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>37.5513585155732</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>7308</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Teno</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>37.1891578249337</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>37.0872982317178</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>37.0538223721192</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>7110</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>36.9818732986884</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Empedrado</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>36.9718309859155</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>36.7633767172813</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>36.6994812544211</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>36.5731101007096</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>7203</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>Pelluhue</t>
         </is>
       </c>
-      <c r="C31">
+      <c r="C105">
+        <v>36.4185474537037</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>36.2377554534839</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>7108</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Río Claro</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>36.202319029042</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>36.2021827161606</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>7307</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>36.1048782514751</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>7110</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>36.0812539987204</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>36.0626244066759</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>35.5272334490032</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>7305</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Rauco</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>35.5151220215565</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>7304</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Molina</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>35.4207537429014</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>35.1964009770201</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>San Javier</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>34.7511156056374</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>34.7114060808609</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Curepto</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>34.4899169632266</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>7302</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Hualañé</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>34.4429169939775</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>7305</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Rauco</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>34.3696630957926</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>34.2647442801658</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>7306</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Romeral</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>34.2323369565217</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Empedrado</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>34.2087312414734</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>34.0520289382071</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Pelarco</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>34.0322137509444</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Villa Alegre</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>33.9559579700425</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Pencahue</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>33.9435146443515</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>33.861024266233</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>7306</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Romeral</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>33.8123103597746</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>7109</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>San Clemente</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>33.7219560327455</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Colbún</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>33.6058972141682</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>7408</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Yerbas Buenas</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>33.3777596588058</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>33.2509779699403</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>33.1791864049929</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Pelarco</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>33.1687540141297</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>7307</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>33.0220679197095</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>7304</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Molina</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>33.0009894511738</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>32.7255910485472</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>32.2677013815712</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Colbún</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>32.102454642476</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>7403</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Longaví</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>31.9831787627754</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Vichuquén</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>31.9785759294266</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>31.9686101762456</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>31.9683435198245</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>31.9227776202009</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>7408</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Yerbas Buenas</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>31.9038294168842</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Chanco</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>31.8617296737442</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>31.7966743974157</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Curepto</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>31.7153130287648</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>7403</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Longaví</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>31.7043944570995</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Curepto</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>31.6344778254649</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>San Javier</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>31.631299734748</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Pencahue</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>31.4672801635992</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Villa Alegre</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>31.3898704358068</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>7109</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>San Clemente</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>31.3017895689715</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>7308</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Teno</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>31.2927825928529</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>31.1661280490351</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>31.160317897248</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>30.7985436144281</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>30.763841946783</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>30.6420581655481</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>30.5079529226375</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>30.4184721553523</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>7302</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Hualañé</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>30.1610135271553</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>30.090680916525</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>30.0704572869832</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Empedrado</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>30.0636942675159</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Chanco</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>30.0478568456097</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>7108</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Río Claro</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>29.9038059389377</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Empedrado</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>29.8723536737235</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>7305</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Rauco</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>29.8267415892227</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>29.1957395073475</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>28.8803299699793</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>28.5599756281367</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>7110</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>28.495</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>28.3353545004655</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Pencahue</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>28.3144850818094</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>27.9788717288717</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>San Javier</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>27.8659570459684</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Pelarco</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>27.7504374453193</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>7302</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Hualañé</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>27.6395173453997</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Curepto</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>27.2849462365591</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>27.254484938058</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>26.9606154552762</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Villa Alegre</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>26.7070142768467</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>7408</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Yerbas Buenas</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>26.5973534971645</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Vichuquén</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>26.440828881334</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Pelluhue</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>26.3040875662733</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>25.9345238095238</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>25.8521118786094</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>7403</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Longaví</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>25.6690292828097</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>7302</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Hualañé</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>25.63183769561</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>25.3784330161235</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Colbún</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>25.2769000781436</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>7109</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>San Clemente</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>25.2640814928951</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>25.0763297444962</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>24.9157974793568</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Chanco</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>24.7991468919535</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Vichuquén</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>24.6712158808933</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>24.1533478842498</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Chanco</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>23.4711706464764</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>23.2276188364013</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Empedrado</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>23.1515151515152</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Pelluhue</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>22.9188619599579</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Vichuquén</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>22.8225942837815</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Curepto</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>22.640428677014</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Pelluhue</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>22.5761659723924</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Pelluhue</t>
+        </is>
+      </c>
+      <c r="C208">
         <v>22.2740535974814</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Pelluhue</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>22.0060856335579</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Chanco</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>19.6010550609957</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Vichuquén</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>18.8749000799361</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>7108</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Río Claro</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>14.7270712108617</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>7307</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>13.649296196466</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>7306</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Romeral</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>13.542497562705</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>7308</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Teno</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>13.2674951915964</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>13.119660833942</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>7304</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Molina</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>12.9051534563534</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>12.7380807032538</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>12.5775915580385</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Pencahue</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>11.968328752781</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>7305</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Rauco</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>11.8879749314532</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>7110</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>11.8714214588001</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>11.71319073827</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>11.6977357612298</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>7109</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>San Clemente</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>11.6627630851306</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C226">
+        <v>11.4043044191872</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>11.3088132895653</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>11.2485716797047</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>San Javier</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>11.0642309594461</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Pelarco</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>10.8566978193146</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>7408</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Yerbas Buenas</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>10.7315598548972</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>10.5705731112897</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Villa Alegre</t>
+        </is>
+      </c>
+      <c r="C233">
+        <v>10.5271502179945</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Colbún</t>
+        </is>
+      </c>
+      <c r="C234">
+        <v>10.2254582614805</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="C235">
+        <v>10.1076007326007</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Vichuquén</t>
+        </is>
+      </c>
+      <c r="C236">
+        <v>9.94645247657296</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>7403</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Longaví</t>
+        </is>
+      </c>
+      <c r="C237">
+        <v>9.73594184306179</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Empedrado</t>
+        </is>
+      </c>
+      <c r="C238">
+        <v>9.668560606060611</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="C239">
+        <v>9.603653887211401</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>7302</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Hualañé</t>
+        </is>
+      </c>
+      <c r="C240">
+        <v>8.905064703257469</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Chanco</t>
+        </is>
+      </c>
+      <c r="C241">
+        <v>8.797614206316929</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="C242">
+        <v>8.70920425375871</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C243">
+        <v>8.39070943001569</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C244">
+        <v>8.07210826384239</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Curepto</t>
+        </is>
+      </c>
+      <c r="C245">
+        <v>7.29710367413775</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Pelluhue</t>
+        </is>
+      </c>
+      <c r="C246">
+        <v>5.89276175213675</v>
       </c>
     </row>
   </sheetData>
